--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -611,31 +611,31 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1.71</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>16520.349609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>59115.6015625</v>
+        <v>58180.5</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>21476.25</v>
@@ -11016,7 +11016,7 @@
         <v>1.71</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.73</v>
+        <v>0.12</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.08</v>
@@ -21262,7 +21262,7 @@
         <v>-1.46</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-1.7</v>
@@ -31426,12 +31426,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-0.54</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>16300.849609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>57792.55078125</v>
+        <v>57393.3515625</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>21181.80078125</v>
@@ -11121,7 +11121,7 @@
         <v>0.36</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.54</v>
+        <v>-1.23</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.3</v>
@@ -21472,7 +21472,7 @@
         <v>-0.86</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.68</v>
@@ -31741,7 +31741,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.06%</t>
         </is>
       </c>
     </row>
@@ -591,51 +591,51 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-3.19</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-3.3</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-4.42</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-4.71</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-4.77</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>15523.7001953125</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>56253.75</v>
+        <v>54761.1015625</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>20233</v>
@@ -11296,7 +11296,7 @@
         <v>-4.42</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-3.19</v>
+        <v>-5.76</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-4.77</v>
@@ -21822,7 +21822,7 @@
         <v>-2.5</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-2.65</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-2.68</v>
@@ -32266,12 +32266,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Next 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-5.35%</t>
+          <t>-5.29%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-6.22</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>15572.599609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>54492.30078125</v>
+        <v>54855.5</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>20226.900390625</v>
@@ -11471,7 +11471,7 @@
         <v>-4.12</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-6.22</v>
+        <v>-5.6</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-4.8</v>
@@ -22172,7 +22172,7 @@
         <v>0.74</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0.59</v>
@@ -32791,12 +32791,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>-4.66%</t>
         </is>
       </c>
     </row>
@@ -631,21 +631,21 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-5.79</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Nifty 500</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-5.88</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="9">
@@ -661,11 +661,11 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 500</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-6.92</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="11">
@@ -782,7 +782,7 @@
         <v>15731.4501953125</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>54087</v>
+        <v>55331.05078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>20397.75</v>
@@ -11576,7 +11576,7 @@
         <v>-3.14</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-6.92</v>
+        <v>-4.78</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-3.99</v>
@@ -22382,7 +22382,7 @@
         <v>2.07</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>2.34</v>
@@ -33106,12 +33106,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-6.54%</t>
+          <t>-6.75%</t>
         </is>
       </c>
     </row>
@@ -591,51 +591,51 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-4.78</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-5</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-5.21</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-6.09</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-6.51</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>15396.099609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>55331.05078125</v>
+        <v>54097.80078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>19952.75</v>
@@ -11611,7 +11611,7 @@
         <v>-5.21</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-4.78</v>
+        <v>-6.9</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-6.09</v>
@@ -22452,7 +22452,7 @@
         <v>-2.13</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-2.18</v>
@@ -33211,12 +33211,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty Midcap 50</t>
+          <t>Nifty 50, Nifty Midcap 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-8.76%</t>
+          <t>-9.01%</t>
         </is>
       </c>
     </row>
@@ -591,51 +591,51 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-6.9</v>
+        <v>-7.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-7.21</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-7.75</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-8.6</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>14983.349609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>54097.80078125</v>
+        <v>52650</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>19430.900390625</v>
@@ -11646,7 +11646,7 @@
         <v>-7.75</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-6.9</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-8.550000000000001</v>
@@ -22522,7 +22522,7 @@
         <v>-2.68</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-2.68</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-2.62</v>
@@ -33316,12 +33316,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-7.16%</t>
+          <t>-7.19%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-7.38</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         <v>15270.5</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>53819.1484375</v>
+        <v>53677.05078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>19805.5</v>
@@ -11716,7 +11716,7 @@
         <v>-5.98</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-7.38</v>
+        <v>-7.63</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-6.78</v>
@@ -22662,7 +22662,7 @@
         <v>-0.16</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.32</v>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.55%</t>
         </is>
       </c>
     </row>
@@ -621,31 +621,31 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty 100</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.87</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty 100</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-1.64</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-1.94</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         <v>16452.400390625</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>56978.75</v>
+        <v>57843.94921875</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>21300.30078125</v>
@@ -11891,7 +11891,7 @@
         <v>1.3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-1.94</v>
+        <v>-0.45</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0.25</v>
@@ -23012,7 +23012,7 @@
         <v>1.27</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.6</v>
@@ -34051,12 +34051,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty Midcap 50</t>
+          <t>Nifty 50, Nifty Midcap 50, Nifty 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-1.3%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.45</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="7">
@@ -782,7 +782,7 @@
         <v>16326.2998046875</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>57843.94921875</v>
+        <v>57513.30078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>21177.599609375</v>
@@ -11926,7 +11926,7 @@
         <v>0.52</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.45</v>
+        <v>-1.02</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.32</v>
@@ -23082,7 +23082,7 @@
         <v>-0.77</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.58</v>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -601,31 +601,31 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty 50</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2.57</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty 50</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="7">
@@ -782,7 +782,7 @@
         <v>17014.599609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>59146.75</v>
+        <v>59898.19921875</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22045.19921875</v>
@@ -12031,7 +12031,7 @@
         <v>4.76</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.79</v>
+        <v>3.08</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>3.76</v>
@@ -23292,7 +23292,7 @@
         <v>1.25</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.22</v>
@@ -34471,12 +34471,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
     </row>
@@ -581,31 +581,31 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 50</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>16741.75</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>59952.80078125</v>
+        <v>59374.80078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>21875.94921875</v>
@@ -12206,7 +12206,7 @@
         <v>3.08</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.17</v>
+        <v>2.18</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>2.96</v>
@@ -23642,7 +23642,7 @@
         <v>-1.15</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-1.01</v>
@@ -34996,7 +34996,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -591,21 +591,21 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.55</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>16882.5</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>60376.8984375</v>
+        <v>59784.8515625</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22000.05078125</v>
@@ -12346,7 +12346,7 @@
         <v>3.94</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.9</v>
+        <v>2.89</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>3.55</v>
@@ -23922,7 +23922,7 @@
         <v>-0.86</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.96</v>
@@ -35416,12 +35416,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty500 Multicap 50:25:25, Nifty 50</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty 200</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.7</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>17628.19921875</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>62003.1484375</v>
+        <v>61910.8984375</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22772.400390625</v>
@@ -12521,7 +12521,7 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>6.7</v>
+        <v>6.54</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>7.18</v>
@@ -24272,7 +24272,7 @@
         <v>0.06</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.14</v>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4.7</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>17273.150390625</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>60839.69921875</v>
+        <v>60567.1484375</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22257.94921875</v>
@@ -12696,7 +12696,7 @@
         <v>6.35</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4.7</v>
+        <v>4.23</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>4.76</v>
@@ -24622,7 +24622,7 @@
         <v>-0.49</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.44</v>
@@ -36466,12 +36466,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>17478.25</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>61300.6015625</v>
+        <v>61389.30078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22504.19921875</v>
@@ -12871,7 +12871,7 @@
         <v>7.61</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>5.92</v>
@@ -24972,7 +24972,7 @@
         <v>0.14</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0.11</v>
@@ -36996,7 +36996,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -591,21 +591,21 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7.66</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>17490.55078125</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>62558.8515625</v>
+        <v>61723.80078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22571.400390625</v>
@@ -13116,7 +13116,7 @@
         <v>7.69</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7.66</v>
+        <v>6.22</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>6.24</v>
@@ -25462,7 +25462,7 @@
         <v>-1.49</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-1.37</v>
@@ -37726,7 +37726,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -591,21 +591,21 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4.92</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4.73</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>17198.900390625</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>60966.6484375</v>
+        <v>60754.8984375</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22251.80078125</v>
@@ -13291,7 +13291,7 @@
         <v>5.89</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4.92</v>
+        <v>4.55</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>4.73</v>
@@ -25812,7 +25812,7 @@
         <v>-0.38</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.29</v>
@@ -38251,12 +38251,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty 50</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.09</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +782,7 @@
         <v>17265.900390625</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>59325.3984375</v>
+        <v>60768.1015625</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22257.900390625</v>
@@ -13466,7 +13466,7 @@
         <v>6.3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2.09</v>
+        <v>4.58</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>4.76</v>
@@ -26162,7 +26162,7 @@
         <v>2.37</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>2.41</v>
@@ -38776,12 +38776,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 50</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Next 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -601,41 +601,41 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4.71</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4.58</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3.84</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3.33</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
@@ -651,11 +651,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="10">
@@ -770,7 +770,7 @@
         <v>24013.099609375</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72356.6484375</v>
+        <v>70007.203125</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25086.650390625</v>
@@ -13629,7 +13629,7 @@
         <v>1.14</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.71</v>
+        <v>1.31</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.23</v>
@@ -26500,7 +26500,7 @@
         <v>-0.64</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>-0.58</v>
@@ -39301,7 +39301,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -605,37 +605,37 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4.58</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3.84</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3.33</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.42</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8">
@@ -651,11 +651,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="10">
@@ -770,7 +770,7 @@
         <v>24013.099609375</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>70007.203125</v>
+        <v>72356.6484375</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25086.650390625</v>
@@ -782,7 +782,7 @@
         <v>17735.30078125</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>60768.1015625</v>
+        <v>62517.30078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22972.94921875</v>
@@ -805,7 +805,7 @@
         <v>24168</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>70007.203125</v>
+        <v>72595.953125</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>25233.650390625</v>
@@ -817,7 +817,7 @@
         <v>17716.849609375</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>60768.1015625</v>
+        <v>62379.25</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>22893.19921875</v>
@@ -840,7 +840,7 @@
         <v>24085.69921875</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>70007.203125</v>
+        <v>72258.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>25141.80078125</v>
@@ -852,7 +852,7 @@
         <v>17659.650390625</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>60768.1015625</v>
+        <v>62123.3515625</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>22786.25</v>
@@ -875,7 +875,7 @@
         <v>23989.150390625</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>70007.203125</v>
+        <v>71798.6484375</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>25029.900390625</v>
@@ -887,7 +887,7 @@
         <v>17607.150390625</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>60768.1015625</v>
+        <v>61802.05078125</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>22671.400390625</v>
@@ -910,7 +910,7 @@
         <v>23853.900390625</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>70007.203125</v>
+        <v>71685.25</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>24907.849609375</v>
@@ -922,7 +922,7 @@
         <v>17501.900390625</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>60768.1015625</v>
+        <v>61549.6484375</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>22585.099609375</v>
@@ -13629,7 +13629,7 @@
         <v>1.14</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1.31</v>
+        <v>4.71</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.23</v>
@@ -13641,7 +13641,7 @@
         <v>9.19</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4.58</v>
+        <v>7.59</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>8.130000000000001</v>
@@ -13664,7 +13664,7 @@
         <v>1.79</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1.31</v>
+        <v>5.05</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.82</v>
@@ -13676,7 +13676,7 @@
         <v>9.08</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4.58</v>
+        <v>7.35</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>7.75</v>
@@ -13699,7 +13699,7 @@
         <v>1.44</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1.31</v>
+        <v>4.57</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.45</v>
@@ -13711,7 +13711,7 @@
         <v>8.73</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>4.58</v>
+        <v>6.91</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>7.25</v>
@@ -13734,7 +13734,7 @@
         <v>1.04</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.31</v>
+        <v>3.9</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -13746,7 +13746,7 @@
         <v>8.41</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4.58</v>
+        <v>6.36</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>6.71</v>
@@ -13769,7 +13769,7 @@
         <v>0.47</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.31</v>
+        <v>3.74</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>-0.48</v>
@@ -13781,7 +13781,7 @@
         <v>7.76</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.58</v>
+        <v>5.92</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>6.3</v>
@@ -26500,7 +26500,7 @@
         <v>-0.64</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>-0.58</v>
@@ -26512,7 +26512,7 @@
         <v>0.1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0.35</v>
@@ -26535,7 +26535,7 @@
         <v>0.34</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.37</v>
@@ -26547,7 +26547,7 @@
         <v>0.32</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0.47</v>
@@ -26570,7 +26570,7 @@
         <v>0.4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.45</v>
@@ -26582,7 +26582,7 @@
         <v>0.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.51</v>
@@ -26605,7 +26605,7 @@
         <v>0.57</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0.49</v>
@@ -26617,7 +26617,7 @@
         <v>0.6</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.38</v>
@@ -26640,7 +26640,7 @@
         <v>0.98</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1.24</v>
@@ -26652,7 +26652,7 @@
         <v>1.37</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>1.47</v>
@@ -39301,7 +39301,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -39316,12 +39316,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -39331,12 +39331,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 150, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>
@@ -39351,7 +39351,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -39361,12 +39361,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -591,21 +591,21 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>7.59</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7.08</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="6">
@@ -770,7 +770,7 @@
         <v>24056</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72356.6484375</v>
+        <v>72199.546875</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25114.099609375</v>
@@ -782,7 +782,7 @@
         <v>17587.849609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>62517.30078125</v>
+        <v>61795.5</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22751.05078125</v>
@@ -805,7 +805,7 @@
         <v>24056</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>72356.6484375</v>
+        <v>72199.546875</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>25114.099609375</v>
@@ -817,7 +817,7 @@
         <v>17587.849609375</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>62517.30078125</v>
+        <v>61795.5</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>22751.05078125</v>
@@ -840,7 +840,7 @@
         <v>24021.650390625</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>72356.6484375</v>
+        <v>72060.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>25075.94921875</v>
@@ -852,7 +852,7 @@
         <v>17690.30078125</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>62517.30078125</v>
+        <v>62135.25</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>22872.5</v>
@@ -875,7 +875,7 @@
         <v>23824.099609375</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>72356.6484375</v>
+        <v>72068.75</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>24907.80078125</v>
@@ -887,7 +887,7 @@
         <v>17639.80078125</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>62517.30078125</v>
+        <v>62070.3515625</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>22853.55078125</v>
@@ -910,7 +910,7 @@
         <v>24102.900390625</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>72356.6484375</v>
+        <v>73073.203125</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25209.55078125</v>
@@ -922,7 +922,7 @@
         <v>17800.44921875</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>62517.30078125</v>
+        <v>62729.1015625</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>23073.05078125</v>
@@ -13804,7 +13804,7 @@
         <v>1.32</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.34</v>
@@ -13816,7 +13816,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7.59</v>
+        <v>6.35</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>7.08</v>
@@ -13839,7 +13839,7 @@
         <v>1.32</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.34</v>
@@ -13851,7 +13851,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>7.59</v>
+        <v>6.35</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>7.08</v>
@@ -13874,7 +13874,7 @@
         <v>1.17</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.71</v>
+        <v>4.28</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.19</v>
@@ -13886,7 +13886,7 @@
         <v>8.92</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7.59</v>
+        <v>6.93</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>7.65</v>
@@ -13909,7 +13909,7 @@
         <v>0.34</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.71</v>
+        <v>4.29</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-0.48</v>
@@ -13921,7 +13921,7 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>7.59</v>
+        <v>6.82</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>7.56</v>
@@ -13944,7 +13944,7 @@
         <v>1.52</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.71</v>
+        <v>5.74</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0.72</v>
@@ -13956,7 +13956,7 @@
         <v>9.6</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.59</v>
+        <v>7.95</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>8.6</v>
@@ -26885,7 +26885,7 @@
         <v>0.14</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.15</v>
@@ -26897,7 +26897,7 @@
         <v>-0.58</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>-0.53</v>
@@ -26920,7 +26920,7 @@
         <v>0.83</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.68</v>
@@ -26932,7 +26932,7 @@
         <v>0.29</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.08</v>
@@ -26955,7 +26955,7 @@
         <v>-1.16</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-1.2</v>
@@ -26967,7 +26967,7 @@
         <v>-0.9</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>-0.95</v>
@@ -26990,7 +26990,7 @@
         <v>0.37</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0.49</v>
@@ -27002,7 +27002,7 @@
         <v>0.37</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.44</v>
@@ -39841,12 +39841,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty 100, Nifty 50, Nifty 200</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 50</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
@@ -39861,7 +39861,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Nifty 100, Nifty 200, Nifty 50</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted, Nifty 500</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty Midcap 100, Nifty 50, Nifty Midcap 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +770,7 @@
         <v>24270.849609375</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72268.953125</v>
+        <v>72199.546875</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25301.900390625</v>
@@ -13979,7 +13979,7 @@
         <v>2.22</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.09</v>
@@ -27200,7 +27200,7 @@
         <v>0.39</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.28</v>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.49%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.35</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +770,7 @@
         <v>24270.849609375</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72199.546875</v>
+        <v>72268.953125</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25301.900390625</v>
@@ -782,7 +782,7 @@
         <v>17783.25</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>61795.5</v>
+        <v>62190.30078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22884.349609375</v>
@@ -805,7 +805,7 @@
         <v>24175.69921875</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>72199.546875</v>
+        <v>72418.546875</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>25230.19921875</v>
@@ -817,7 +817,7 @@
         <v>17806</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>61795.5</v>
+        <v>62307.8984375</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>22934.900390625</v>
@@ -840,7 +840,7 @@
         <v>24005.849609375</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>72199.546875</v>
+        <v>72100.6484375</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>25065.099609375</v>
@@ -852,7 +852,7 @@
         <v>17716.099609375</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>61795.5</v>
+        <v>62008.80078125</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>22823.5</v>
@@ -875,7 +875,7 @@
         <v>23865.75</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>72199.546875</v>
+        <v>71629.453125</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>24915.599609375</v>
@@ -887,7 +887,7 @@
         <v>17594.900390625</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>61795.5</v>
+        <v>61797.69921875</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>22774.25</v>
@@ -910,7 +910,7 @@
         <v>23946.25</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>72199.546875</v>
+        <v>71510.296875</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>24976.69921875</v>
@@ -922,7 +922,7 @@
         <v>17521</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>61795.5</v>
+        <v>61567.30078125</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>22679.650390625</v>
@@ -13979,7 +13979,7 @@
         <v>2.22</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.09</v>
@@ -13991,7 +13991,7 @@
         <v>9.49</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>6.35</v>
+        <v>7.03</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>7.71</v>
@@ -14014,7 +14014,7 @@
         <v>1.82</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4.48</v>
+        <v>4.8</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.8</v>
@@ -14026,7 +14026,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>6.35</v>
+        <v>7.23</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>7.95</v>
@@ -14049,7 +14049,7 @@
         <v>1.11</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.48</v>
+        <v>4.34</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.15</v>
@@ -14061,7 +14061,7 @@
         <v>9.08</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6.35</v>
+        <v>6.71</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>7.42</v>
@@ -14084,7 +14084,7 @@
         <v>0.52</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.48</v>
+        <v>3.66</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-0.45</v>
@@ -14119,7 +14119,7 @@
         <v>0.86</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.48</v>
+        <v>3.48</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>-0.21</v>
@@ -14131,7 +14131,7 @@
         <v>7.87</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.35</v>
+        <v>5.95</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>6.75</v>
@@ -27200,7 +27200,7 @@
         <v>0.39</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.28</v>
@@ -27212,7 +27212,7 @@
         <v>-0.13</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.22</v>
@@ -27235,7 +27235,7 @@
         <v>0.71</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.66</v>
@@ -27247,7 +27247,7 @@
         <v>0.51</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0.49</v>
@@ -27270,7 +27270,7 @@
         <v>0.59</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.6</v>
@@ -27282,7 +27282,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.22</v>
@@ -27305,7 +27305,7 @@
         <v>-0.34</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-0.24</v>
@@ -27317,7 +27317,7 @@
         <v>0.42</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0.42</v>
@@ -27340,7 +27340,7 @@
         <v>-0.46</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>-0.55</v>
@@ -27352,7 +27352,7 @@
         <v>-0.38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>-0.31</v>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>
@@ -40381,12 +40381,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty 100, Nifty 50</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty 100</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -40396,7 +40396,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -40411,12 +40411,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nifty 100, Nifty500 Multicap 50:25:25, Nifty 200</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.86%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +770,7 @@
         <v>24206.900390625</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72391.796875</v>
+        <v>72268.953125</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25255.099609375</v>
@@ -14154,7 +14154,7 @@
         <v>1.95</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.9</v>
@@ -27550,7 +27550,7 @@
         <v>1.02</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.06</v>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty Next 50, Nifty 50</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7.03</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +770,7 @@
         <v>24206.900390625</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72268.953125</v>
+        <v>72391.796875</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25255.099609375</v>
@@ -782,7 +782,7 @@
         <v>18059.5</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>62190.30078125</v>
+        <v>63036.80078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>23166.5</v>
@@ -805,7 +805,7 @@
         <v>23962.80078125</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>72268.953125</v>
+        <v>71485.8515625</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>24989.25</v>
@@ -817,7 +817,7 @@
         <v>17844.5</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>62190.30078125</v>
+        <v>62166.8515625</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>22855.75</v>
@@ -840,7 +840,7 @@
         <v>23882.05078125</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>72268.953125</v>
+        <v>70898.75</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>24883.05078125</v>
@@ -852,7 +852,7 @@
         <v>17604.44921875</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>62190.30078125</v>
+        <v>61322.75</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>22537.849609375</v>
@@ -875,7 +875,7 @@
         <v>24398.69921875</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>72268.953125</v>
+        <v>72248.453125</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>25409.650390625</v>
@@ -887,7 +887,7 @@
         <v>17864.05078125</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>62190.30078125</v>
+        <v>62285.30078125</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>22912.30078125</v>
@@ -910,7 +910,7 @@
         <v>24430.349609375</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>72268.953125</v>
+        <v>72685.6015625</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25464.44921875</v>
@@ -922,7 +922,7 @@
         <v>17863.55078125</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>62190.30078125</v>
+        <v>62471.5</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>22973.349609375</v>
@@ -14154,7 +14154,7 @@
         <v>1.95</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.9</v>
@@ -14166,7 +14166,7 @@
         <v>11.19</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7.03</v>
+        <v>8.48</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>9.039999999999999</v>
@@ -14189,7 +14189,7 @@
         <v>0.93</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4.58</v>
+        <v>3.45</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>-0.16</v>
@@ -14201,7 +14201,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>7.03</v>
+        <v>6.98</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>7.57</v>
@@ -14224,7 +14224,7 @@
         <v>0.59</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.58</v>
+        <v>2.6</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>-0.58</v>
@@ -14236,7 +14236,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7.03</v>
+        <v>5.53</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6.08</v>
@@ -14259,7 +14259,7 @@
         <v>2.76</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1.52</v>
@@ -14271,7 +14271,7 @@
         <v>9.99</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>7.03</v>
+        <v>7.19</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>7.84</v>
@@ -14294,7 +14294,7 @@
         <v>2.9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.58</v>
+        <v>5.18</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1.74</v>
@@ -14306,7 +14306,7 @@
         <v>9.98</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.03</v>
+        <v>7.51</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>8.130000000000001</v>
@@ -27550,7 +27550,7 @@
         <v>1.02</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.06</v>
@@ -27562,7 +27562,7 @@
         <v>1.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.36</v>
@@ -27585,7 +27585,7 @@
         <v>0.34</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.43</v>
@@ -27597,7 +27597,7 @@
         <v>1.36</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1.41</v>
@@ -27620,7 +27620,7 @@
         <v>-2.12</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>-2.07</v>
@@ -27632,7 +27632,7 @@
         <v>-1.45</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>-1.55</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-1.63</v>
@@ -27655,7 +27655,7 @@
         <v>-0.13</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-0.22</v>
@@ -27667,7 +27667,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>-0.27</v>
@@ -27690,7 +27690,7 @@
         <v>0.66</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0.64</v>
@@ -27702,7 +27702,7 @@
         <v>0.45</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0.39</v>
@@ -40876,12 +40876,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Midcap 50</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -40891,12 +40891,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 150, Nifty Midcap 100, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -40906,7 +40906,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 50</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -40921,12 +40921,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 50, Nifty Midcap 100</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty 100</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted, Nifty 500</t>
+          <t>Nifty Next 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
     </row>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Midcap 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
@@ -621,21 +621,21 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.1</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="8">
@@ -770,7 +770,7 @@
         <v>24334.30078125</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>71828.3984375</v>
+        <v>72391.796875</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25327.650390625</v>
@@ -14329,7 +14329,7 @@
         <v>2.49</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3.94</v>
+        <v>4.76</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.19</v>
@@ -27900,7 +27900,7 @@
         <v>1.09</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.87</v>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
@@ -591,21 +591,21 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100</t>
+          <t>Nifty Midcap 150</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>8.48</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150</t>
+          <t>Nifty Midcap 100</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>8.1</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="5">
@@ -621,21 +621,21 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Nifty Next 50</t>
+          <t>Nifty 200</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.76</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nifty 200</t>
+          <t>Nifty Next 50</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="8">
@@ -770,7 +770,7 @@
         <v>24334.30078125</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72391.796875</v>
+        <v>71828.3984375</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>25327.650390625</v>
@@ -782,7 +782,7 @@
         <v>17930.849609375</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>63036.80078125</v>
+        <v>62428.05078125</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>22967.900390625</v>
@@ -805,7 +805,7 @@
         <v>24072.75</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>72391.796875</v>
+        <v>71896.75</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>25109.19921875</v>
@@ -817,7 +817,7 @@
         <v>17985.099609375</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>63036.80078125</v>
+        <v>62686.75</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>23060.05078125</v>
@@ -840,7 +840,7 @@
         <v>24078.5</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>72391.796875</v>
+        <v>72148.796875</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>25130.099609375</v>
@@ -852,7 +852,7 @@
         <v>18036.75</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>63036.80078125</v>
+        <v>62943.19921875</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>23153.400390625</v>
@@ -875,7 +875,7 @@
         <v>24052.05078125</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>72391.796875</v>
+        <v>71851.6015625</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>25088.650390625</v>
@@ -887,7 +887,7 @@
         <v>17988.150390625</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>63036.80078125</v>
+        <v>62766.3984375</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>23053.599609375</v>
@@ -910,7 +910,7 @@
         <v>24211</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>72391.796875</v>
+        <v>72111.3984375</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25240.80078125</v>
@@ -922,7 +922,7 @@
         <v>18089.55078125</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>63036.80078125</v>
+        <v>63040.94921875</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>23167.400390625</v>
@@ -14329,7 +14329,7 @@
         <v>2.49</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.76</v>
+        <v>3.94</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.19</v>
@@ -14341,7 +14341,7 @@
         <v>10.4</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>8.48</v>
+        <v>7.43</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>8.1</v>
@@ -14364,7 +14364,7 @@
         <v>1.39</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4.76</v>
+        <v>4.04</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.32</v>
@@ -14376,7 +14376,7 @@
         <v>10.73</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>8.48</v>
+        <v>7.88</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>8.539999999999999</v>
@@ -14399,7 +14399,7 @@
         <v>1.41</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.76</v>
+        <v>4.41</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.4</v>
@@ -14411,7 +14411,7 @@
         <v>11.05</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>8.48</v>
+        <v>8.32</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>8.98</v>
@@ -14434,7 +14434,7 @@
         <v>1.3</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.76</v>
+        <v>3.98</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0.24</v>
@@ -14446,7 +14446,7 @@
         <v>10.75</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>8.48</v>
+        <v>8.02</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>8.51</v>
@@ -14469,7 +14469,7 @@
         <v>1.97</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.76</v>
+        <v>4.35</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0.85</v>
@@ -14481,7 +14481,7 @@
         <v>11.38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>9.039999999999999</v>
@@ -27900,7 +27900,7 @@
         <v>1.09</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.87</v>
@@ -27912,7 +27912,7 @@
         <v>-0.3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-0.4</v>
@@ -27935,7 +27935,7 @@
         <v>-0.02</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>-0.08</v>
@@ -27947,7 +27947,7 @@
         <v>-0.29</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>-0.4</v>
@@ -27970,7 +27970,7 @@
         <v>0.11</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.17</v>
@@ -27982,7 +27982,7 @@
         <v>0.27</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.43</v>
@@ -28005,7 +28005,7 @@
         <v>-0.66</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-0.6</v>
@@ -28017,7 +28017,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>-0.49</v>
@@ -28040,7 +28040,7 @@
         <v>0.02</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>-0.06</v>
@@ -28052,7 +28052,7 @@
         <v>0.17</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Midcap 50</t>
         </is>
       </c>
     </row>
@@ -41416,12 +41416,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 100, Nifty Midcap 150, Nifty Next 50</t>
         </is>
       </c>
     </row>
@@ -41431,12 +41431,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
+          <t>Nifty Midcap 150, Nifty Next 50, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 100, Nifty 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>
@@ -41461,12 +41461,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty 50, Nifty Next 50</t>
+          <t>Nifty Midcap 50, Nifty 50, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 100, Nifty 200</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="3">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="6">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -767,34 +767,34 @@
         <v>46227</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>23767.44921875</v>
+        <v>23869.599609375</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>71766</v>
+        <v>71828.3984375</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>24840.75</v>
+        <v>24932.5</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13762.400390625</v>
+        <v>13805.849609375</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>17709.44921875</v>
+        <v>17690.5</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>62428.05078125</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>22685.25</v>
+        <v>22705.25</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>22913.30078125</v>
+        <v>22982.400390625</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>16.3799991607666</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22913.30078125</v>
+        <v>22982.400390625</v>
       </c>
     </row>
     <row r="3">
@@ -14501,34 +14501,34 @@
         <v>46227</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.38</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>7.43</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>3.08</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="3">
@@ -28247,34 +28247,34 @@
         <v>46227</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-0.43</v>
+        <v>0</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>-0.3</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -41926,12 +41926,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Next 50</t>
+          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty Next 50</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.87</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="5">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-0.38</v>
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -767,34 +767,34 @@
         <v>46227</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>23869.599609375</v>
+        <v>23767.44921875</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>71828.3984375</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>24932.5</v>
+        <v>24840.75</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>13805.849609375</v>
+        <v>13762.400390625</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>17690.5</v>
+        <v>17709.44921875</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>62428.05078125</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>22705.25</v>
+        <v>22685.25</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>22982.400390625</v>
+        <v>22913.30078125</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>16.3799991607666</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>22982.400390625</v>
+        <v>22913.30078125</v>
       </c>
     </row>
     <row r="3">
@@ -14501,34 +14501,34 @@
         <v>46227</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>3.94</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.38</v>
+        <v>-0.75</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>7.43</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>6.87</v>
+        <v>6.77</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>3.08</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="3">
@@ -28247,34 +28247,34 @@
         <v>46227</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>-0.3</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3">
@@ -41926,12 +41926,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty Next 50, Nifty 100</t>
+          <t>Nifty Midcap 50, Nifty Next 50, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty Next 50</t>
+          <t>Nifty 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>6.24%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         <v>23594.900390625</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>16.92000007629395</v>
+        <v>16.93000030517578</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>23594.900390625</v>
@@ -826,7 +826,7 @@
         <v>23658.099609375</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>16.94000053405762</v>
+        <v>16.93000030517578</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>23658.099609375</v>
@@ -15050,7 +15050,7 @@
         <v>3.4</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>3.4</v>
@@ -15085,7 +15085,7 @@
         <v>3.67</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6.61</v>
+        <v>6.54</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>3.67</v>
@@ -29321,7 +29321,7 @@
         <v>-0.27</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>-0.27</v>
@@ -29356,7 +29356,7 @@
         <v>-0.06</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>-0.06</v>
@@ -43501,7 +43501,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 100, Nifty 50, Nifty500 Multicap 50:25:25</t>
+          <t>Nifty Midcap 100, Nifty500 Multicap 50:25:25, Nifty 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>5.83%</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>12.54</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10.39</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6.61</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
@@ -764,37 +764,37 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>24287.650390625</v>
+        <v>24154.900390625</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>74474.1015625</v>
+        <v>74308.8984375</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>25457.30078125</v>
+        <v>25333.650390625</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>14133.849609375</v>
+        <v>14066.650390625</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>18279</v>
+        <v>18216.80078125</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>62428.05078125</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>23454.94921875</v>
+        <v>23364.900390625</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>23564.44921875</v>
+        <v>23472.400390625</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>16.94000053405762</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>23564.44921875</v>
+        <v>23472.400390625</v>
       </c>
     </row>
     <row r="3">
@@ -15058,37 +15058,37 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>12.54</v>
+        <v>12.16</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>7.43</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>10.39</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6.61</v>
+        <v>6.67</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="3">
@@ -29364,37 +29364,37 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.87</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.26</v>
+        <v>-0.75</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.15</v>
+        <v>-0.24</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.52</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="3">
@@ -43602,11 +43602,11 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Midcap 50</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 100, Nifty Next 50</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.82%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6.29</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>23530.30078125</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.88999938964844</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>23530.30078125</v>
@@ -13970,7 +13970,7 @@
         <v>3.11</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>6.29</v>
+        <v>6.36</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>3.11</v>
@@ -27180,7 +27180,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0.07000000000000001</v>
@@ -40315,7 +40315,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty 200</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.74%</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6.86</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="6">
@@ -772,7 +772,7 @@
         <v>23482</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>16.97999954223633</v>
+        <v>16.88999938964844</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>23482</v>
@@ -804,7 +804,7 @@
         <v>23482</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>16.97999954223633</v>
+        <v>16.88999938964844</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>23482</v>
@@ -14130,7 +14130,7 @@
         <v>2.9</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>6.86</v>
+        <v>6.29</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>2.9</v>
@@ -14162,7 +14162,7 @@
         <v>2.9</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6.86</v>
+        <v>6.29</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>2.9</v>
@@ -27532,7 +27532,7 @@
         <v>-0.33</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>-0.33</v>
@@ -40805,12 +40805,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty Midcap 50, Nifty Midcap 150</t>
+          <t>Nifty Midcap 50, Nifty Midcap 150, Nifty Next 50</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty 200</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
     </row>

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5.66</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         <v>23254.150390625</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>16.79000091552734</v>
+        <v>16.75</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>23254.150390625</v>
@@ -826,7 +826,7 @@
         <v>23254.05078125</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>16.68000030517578</v>
+        <v>16.75</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>23254.05078125</v>
@@ -15575,7 +15575,7 @@
         <v>1.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>5.66</v>
+        <v>5.41</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1.9</v>
@@ -15610,7 +15610,7 @@
         <v>1.9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4.97</v>
+        <v>5.41</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>1.9</v>
@@ -30371,7 +30371,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0</v>
@@ -30406,7 +30406,7 @@
         <v>0.13</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0.13</v>
@@ -45076,7 +45076,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
+          <t>Nifty 50, Nifty 100, Nifty Midcap 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -45091,7 +45091,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty Midcap 50, Nifty Next 50</t>
+          <t>Nifty Midcap 150, Nifty500 Multicap 50:25:25, Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.83%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         <v>23254.150390625</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>16.75</v>
+        <v>16.79000091552734</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>23254.150390625</v>
@@ -15575,7 +15575,7 @@
         <v>1.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1.9</v>
@@ -30371,7 +30371,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0</v>
@@ -45076,7 +45076,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty 50, Nifty 100, Nifty Midcap 100</t>
+          <t>Nifty500 Multicap 50:25:25, Nifty 50, Nifty 100</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/nse_indices_1_dashboard.xlsx
+++ b/nse_indices_1_dashboard.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         <v>22866.5</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>16.51000022888184</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>22866.5</v>
@@ -826,7 +826,7 @@
         <v>22952.349609375</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>16.60000038146973</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>22952.349609375</v>
@@ -15750,7 +15750,7 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.2</v>
@@ -15785,7 +15785,7 @@
         <v>0.58</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4.47</v>
+        <v>4.03</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0.58</v>
@@ -30721,7 +30721,7 @@
         <v>-0.37</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>-0.37</v>
@@ -30756,7 +30756,7 @@
         <v>-0.03</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>-0.03</v>
@@ -45601,12 +45601,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty Midcap 150</t>
+          <t>Nifty Midcap 50, Nifty Midcap 100, Nifty500 Multicap 50:25:25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty 100</t>
+          <t>Nifty Next 50, Nifty 100, Nifty500 LargeMidSmall Equal-Cap Weighted</t>
         </is>
       </c>
     </row>
@@ -45621,7 +45621,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Nifty Next 50, Nifty Midcap 150, Nifty Midcap 50</t>
+          <t>Nifty Next 50, Nifty500 Multicap 50:25:25, Nifty Midcap 150</t>
         </is>
       </c>
     </row>
